--- a/output/感染症対策委員会運営要綱_いいかいご.xlsx
+++ b/output/感染症対策委員会運営要綱_いいかいご.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1404,124 +1404,104 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>感染症対策全体の統括・研修・教育担当を兼務</t>
+          <t>感染症対策全体の統括・最終判断・行政報告。研修・教育担当を兼務</t>
         </is>
       </c>
       <c r="E134" s="12" t="n"/>
     </row>
-    <row r="135" ht="20" customHeight="1">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>副委員長（サービス提供責任者）</t>
+          <t>委員（代表取締役）</t>
         </is>
       </c>
       <c r="B135" s="10" t="n"/>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>岩谷</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>現場調整・周知・実務統括</t>
+          <t>法人としての方針決定、BCPの承認、重大事案時の対外対応</t>
         </is>
       </c>
       <c r="E135" s="12" t="n"/>
     </row>
-    <row r="136" ht="20" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>看護職委員</t>
+          <t>委員（事務・総務）</t>
         </is>
       </c>
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>松本</t>
+          <t>吉田 麻美</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>医療的助言・PPE指導</t>
+          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E136" s="12" t="n"/>
     </row>
-    <row r="137" ht="20" customHeight="1">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>ヘルパー代表</t>
+          <t>委員（ヘルパー代表）</t>
         </is>
       </c>
       <c r="B137" s="10" t="n"/>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>松川</t>
+          <t>WIN YADANAR AWNG</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック</t>
+          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
         </is>
       </c>
       <c r="E137" s="12" t="n"/>
     </row>
-    <row r="138" ht="20" customHeight="1">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>事務・総務</t>
+          <t>顧問（任意）</t>
         </is>
       </c>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>鳥羽</t>
+          <t>主治医・外部専門家・保健所等</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>記録整備・行政書類確認</t>
+          <t>医療的助言・PPE指導（必要に応じて）</t>
         </is>
       </c>
       <c r="E138" s="12" t="n"/>
     </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>研修・教育担当</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="n"/>
-      <c r="C139" s="11" t="inlineStr">
-        <is>
-          <t>生田 友哉（兼務）</t>
-        </is>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>感染研修の企画・欠席者フォロー</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="n"/>
-    </row>
-    <row r="140" ht="8" customHeight="1"/>
+    <row r="139" ht="8" customHeight="1"/>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
     <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="14" t="inlineStr">
-        <is>
-          <t>＜附則＞</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>本資料は、令和8年2月1日から適用する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="107">
-    <mergeCell ref="A142:E142"/>
+  <mergeCells count="105">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A79:E79"/>
@@ -1560,7 +1540,6 @@
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="D53:E53"/>
-    <mergeCell ref="A139:B139"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
@@ -1577,7 +1556,6 @@
     <mergeCell ref="A110:E110"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D139:E139"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="A25:E25"/>
@@ -1618,6 +1596,7 @@
     <mergeCell ref="D137:E137"/>
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A134:B134"/>

--- a/output/感染症対策委員会運営要綱_いいかいご.xlsx
+++ b/output/感染症対策委員会運営要綱_いいかいご.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1428,21 +1428,21 @@
       </c>
       <c r="E135" s="12" t="n"/>
     </row>
-    <row r="136" ht="32" customHeight="1">
+    <row r="136" ht="48" customHeight="1">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>委員（事務・総務）</t>
+          <t>看護職委員</t>
         </is>
       </c>
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>吉田 麻美</t>
+          <t>松村 知恵</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
+          <t>医療的助言・トリアージ・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
         </is>
       </c>
       <c r="E136" s="12" t="n"/>
@@ -1450,18 +1450,18 @@
     <row r="137" ht="32" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>委員（ヘルパー代表）</t>
+          <t>委員（事務・総務）</t>
         </is>
       </c>
       <c r="B137" s="10" t="n"/>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>吉田 麻美</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E137" s="12" t="n"/>
@@ -1469,39 +1469,59 @@
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>顧問（任意）</t>
+          <t>委員（ヘルパー代表）</t>
         </is>
       </c>
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="11" t="inlineStr">
         <is>
+          <t>WIN YADANAR AWNG</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n"/>
+    </row>
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>顧問（任意）</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
           <t>主治医・外部専門家・保健所等</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>医療的助言・PPE指導（必要に応じて）</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="n"/>
-    </row>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="14" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>専門的助言（必要に応じて）</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="n"/>
+    </row>
+    <row r="140" ht="8" customHeight="1"/>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="14" t="inlineStr">
         <is>
           <t>＜附則＞</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>本資料は、令和8年2月1日から適用する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="107">
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A79:E79"/>
@@ -1540,6 +1560,7 @@
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="D53:E53"/>
+    <mergeCell ref="A139:B139"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
@@ -1556,6 +1577,7 @@
     <mergeCell ref="A110:E110"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D139:E139"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="A25:E25"/>
@@ -1596,7 +1618,6 @@
     <mergeCell ref="D137:E137"/>
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A134:B134"/>

--- a/output/感染症対策委員会運営要綱_いいかいご.xlsx
+++ b/output/感染症対策委員会運営要綱_いいかいご.xlsx
@@ -1404,45 +1404,45 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>感染症対策全体の統括・最終判断・行政報告。研修・教育担当を兼務</t>
+          <t>感染症対策全体の統括・最終判断・行政報告、研修講師・欠席者の補講</t>
         </is>
       </c>
       <c r="E134" s="12" t="n"/>
     </row>
-    <row r="135" ht="32" customHeight="1">
+    <row r="135" ht="48" customHeight="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>委員（代表取締役）</t>
+          <t>看護職委員</t>
         </is>
       </c>
       <c r="B135" s="10" t="n"/>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>松村 知恵</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>法人としての方針決定、BCPの承認、重大事案時の対外対応</t>
+          <t>トリアージ・医療的助言・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
         </is>
       </c>
       <c r="E135" s="12" t="n"/>
     </row>
-    <row r="136" ht="48" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>看護職委員</t>
+          <t>委員（代表取締役）</t>
         </is>
       </c>
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>松村 知恵</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>医療的助言・トリアージ・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
+          <t>感染疑い時の訪問調整（担当者限定・訪問順の変更）、BCPの承認</t>
         </is>
       </c>
       <c r="E136" s="12" t="n"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
+          <t>行政報告ルートの確認、議事録・記録整備、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E137" s="12" t="n"/>
@@ -1469,7 +1469,7 @@
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>委員（ヘルパー代表）</t>
+          <t>委員（研修・教育担当）</t>
         </is>
       </c>
       <c r="B138" s="10" t="n"/>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+          <t>研修の体系化、欠席者へのフォロー、現場情報の共有</t>
         </is>
       </c>
       <c r="E138" s="12" t="n"/>

--- a/output/感染症対策委員会運営要綱_いいかいご.xlsx
+++ b/output/感染症対策委員会運営要綱_いいかいご.xlsx
@@ -1475,7 +1475,7 @@
       <c r="B138" s="10" t="n"/>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>WIN YADANAR AUNG</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">

--- a/output/感染症対策委員会運営要綱_いいかいご.xlsx
+++ b/output/感染症対策委員会運営要綱_いいかいご.xlsx
@@ -1437,7 +1437,7 @@
       <c r="B136" s="10" t="n"/>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>吉田 駿成</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
